--- a/visualization/2_team_stats.xlsx
+++ b/visualization/2_team_stats.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mateusz\Desktop\ZBIORCZE\TECH\ANALIZA DANYCH\SQL\VS\Projekty MB\SQL Analysis of International Football Results\visualization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mateusz\Desktop\ZBIORCZE\TECH\ANALIZA DANYCH\SQL\Projekty MB\SQL-Analysis-of-International-Football-Results\visualization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E3BAD1-A5B5-44BA-A214-254E45E4EEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894715CF-8915-479E-BBBB-12DBF70C96BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Top scorers" sheetId="1" state="hidden" r:id="rId1"/>
@@ -2183,35 +2183,9 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="74000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="83000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="30000"/>
-                <a:lumOff val="70000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="1"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -2573,35 +2547,9 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="74000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="83000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="30000"/>
-                <a:lumOff val="70000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="1"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -2953,35 +2901,9 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="74000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="83000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="30000"/>
-                <a:lumOff val="70000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="1"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -3333,35 +3255,9 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="74000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="83000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="30000"/>
-                <a:lumOff val="70000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="1"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -3702,35 +3598,9 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="74000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="83000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="30000"/>
-                <a:lumOff val="70000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="1"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -4439,35 +4309,9 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="74000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="83000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="30000"/>
-                <a:lumOff val="70000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="1"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -4511,7 +4355,7 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:sysClr val="window" lastClr="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -4906,35 +4750,9 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="74000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="83000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="30000"/>
-                <a:lumOff val="70000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="1"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -9455,7 +9273,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9301370" cy="6071152"/>
+    <xdr:ext cx="9291941" cy="6069654"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Wykres 1">
@@ -9488,7 +9306,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9301370" cy="6071152"/>
+    <xdr:ext cx="9291941" cy="6069654"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Wykres 1">
@@ -9521,7 +9339,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9301370" cy="6071152"/>
+    <xdr:ext cx="9291941" cy="6069654"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Wykres 1">
@@ -9554,7 +9372,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9301370" cy="6071152"/>
+    <xdr:ext cx="9291941" cy="6069654"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Wykres 1">
@@ -9587,7 +9405,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9301370" cy="6071152"/>
+    <xdr:ext cx="9291941" cy="6069654"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Wykres 1">
@@ -9620,7 +9438,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9301370" cy="6071152"/>
+    <xdr:ext cx="9291941" cy="6069654"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Wykres 1">
@@ -9653,7 +9471,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9301370" cy="6071152"/>
+    <xdr:ext cx="9291941" cy="6069654"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Wykres 1">
